--- a/x_test.xlsx
+++ b/x_test.xlsx
@@ -425,1046 +425,1214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>is_peak_season</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_rolling_std_5W</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_percentage_4_W</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_rolling_median_10W</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_5W</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_5W</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_4W</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_min_2W</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_percentage_12_W</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_min_3W</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_rolling_std_3W</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_std_5W</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_percentage_3_W</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Settimana_cos</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_percentage_8_W</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_percentage_4_W</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_percentage_2_W</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Sellout_rolling_median_5W</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_min_5W</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_max_3W</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_std_3W</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_3W</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_max_2W</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Sellout_rolling_max_5W</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_percentage_4_W</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_median_10W</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_rolling_max_3W</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Settimana_sin</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_max_10W</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Sellout_rolling_min_10W</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Prezzo_rolling_min_3W</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Sellout_3W</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_rolling_min_3W</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_percentage_3_W</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_4W</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_max_10W</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_rolling_std_3W</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_percentage_4_W</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_min_5W</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_percentage_8_W</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_max_3W</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Prezzo_4W</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_max_2W</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_rolling_max_3W</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_rolling_median_10W</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Settimana_sin</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_3W</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_median_10W</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_min_3W</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_std_3W</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_5W</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_min_2W</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_5W</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Settimana_cos</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_percentage_12_W</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_min_10W</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_rolling_std_5W</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Sellout_percentage_2_W</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Prezzo_rolling_std_5W</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1178</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1388</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2968299711815562</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="E2" t="n">
-        <v>1164</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F2" t="n">
-        <v>218</v>
+        <v>7.553286605600419</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.253822629969419</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H2" t="n">
-        <v>1308</v>
+        <v>7.236339342754344</v>
       </c>
       <c r="I2" t="n">
-        <v>2492</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1115241635687731</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="L2" t="n">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>5.7194114829207</v>
       </c>
       <c r="N2" t="n">
-        <v>1178</v>
+        <v>-0.5327510917030568</v>
       </c>
       <c r="O2" t="n">
-        <v>218</v>
+        <v>0.2595117970697999</v>
       </c>
       <c r="P2" t="n">
-        <v>1178</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="Q2" t="n">
-        <v>218</v>
+        <v>-0.6468646864686469</v>
       </c>
       <c r="R2" t="n">
-        <v>218</v>
+        <v>-0.4184782608695652</v>
       </c>
       <c r="S2" t="n">
-        <v>0.989932495087353</v>
+        <v>7.1770187659099</v>
       </c>
       <c r="T2" t="n">
-        <v>218</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="U2" t="n">
-        <v>1647</v>
+        <v>7.1770187659099</v>
       </c>
       <c r="V2" t="n">
-        <v>976</v>
+        <v>4.387090405450356</v>
       </c>
       <c r="W2" t="n">
-        <v>112.8007092176263</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="X2" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>976</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="Z2" t="n">
-        <v>1388</v>
+        <v>7.553286605600419</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.141540295217043</v>
+        <v>7.569927655242652</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="AC2" t="n">
-        <v>976</v>
+        <v>0.9657399376548549</v>
       </c>
       <c r="AD2" t="n">
-        <v>157.2615655524252</v>
+        <v>7.821242083523558</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1615120274914089</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>5.389071729816501</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>7.1770187659099</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.389071729816501</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1308</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.345565749235474</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="E3" t="n">
-        <v>1178</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F3" t="n">
-        <v>218</v>
+        <v>7.236339342754344</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2646048109965635</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H3" t="n">
-        <v>1164</v>
+        <v>7.1770187659099</v>
       </c>
       <c r="I3" t="n">
-        <v>2492</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="L3" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.064249142413335</v>
       </c>
       <c r="N3" t="n">
-        <v>1178</v>
+        <v>-0.5217391304347826</v>
       </c>
       <c r="O3" t="n">
-        <v>218</v>
+        <v>0.141540295217043</v>
       </c>
       <c r="P3" t="n">
-        <v>976</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="Q3" t="n">
-        <v>218</v>
+        <v>-0.6157205240174672</v>
       </c>
       <c r="R3" t="n">
-        <v>218</v>
+        <v>-0.2845528455284553</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9997685019798909</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="T3" t="n">
-        <v>218</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="U3" t="n">
-        <v>1348</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="V3" t="n">
-        <v>856</v>
+        <v>4.734448753813639</v>
       </c>
       <c r="W3" t="n">
-        <v>162.7308616499428</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="X3" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>856</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="Z3" t="n">
-        <v>1308</v>
+        <v>7.236339342754344</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02151609743622225</v>
+        <v>7.407317710469417</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="AC3" t="n">
-        <v>856</v>
+        <v>0.989932495087353</v>
       </c>
       <c r="AD3" t="n">
-        <v>179.0888047868982</v>
+        <v>7.821242083523558</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.2733446519524618</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>5.389071729816501</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7.060476365999801</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>5.389071729816501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1178</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1597938144329897</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>976</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F4" t="n">
-        <v>218</v>
+        <v>7.1770187659099</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.169779286926995</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H4" t="n">
-        <v>1178</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="I4" t="n">
-        <v>2492</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="J4" t="n">
-        <v>4.618802153517404</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03669724770642202</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="L4" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.193450089155427</v>
       </c>
       <c r="N4" t="n">
-        <v>978</v>
+        <v>-0.4308943089430894</v>
       </c>
       <c r="O4" t="n">
-        <v>218</v>
+        <v>0.02151609743622225</v>
       </c>
       <c r="P4" t="n">
-        <v>978</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="Q4" t="n">
-        <v>226</v>
+        <v>-0.6195652173913043</v>
       </c>
       <c r="R4" t="n">
-        <v>218</v>
+        <v>-0.3457943925233645</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9951053111006976</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="T4" t="n">
-        <v>218</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="U4" t="n">
-        <v>1243</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="V4" t="n">
-        <v>856</v>
+        <v>5.098223992264701</v>
       </c>
       <c r="W4" t="n">
-        <v>69.86653944008418</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="X4" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>856</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="Z4" t="n">
-        <v>1164</v>
+        <v>7.1770187659099</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.09882013873287143</v>
+        <v>7.207118856207756</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="AC4" t="n">
-        <v>856</v>
+        <v>0.9997685019798909</v>
       </c>
       <c r="AD4" t="n">
-        <v>137.6183127348963</v>
+        <v>7.821242083523558</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002049180327868827</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.577708763999919</v>
+        <v>5.389071729816501</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>7.072421900537371</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>5.389071729816501</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>301</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1178</v>
+        <v>1.521198603080359</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08149405772495755</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>856</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F5" t="n">
-        <v>218</v>
+        <v>7.060476365999801</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1086065573770492</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H5" t="n">
-        <v>976</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="I5" t="n">
-        <v>2492</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="J5" t="n">
-        <v>4.618802153517404</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03669724770642202</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="L5" t="n">
-        <v>856</v>
+        <v>1.726118501244531</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03669724770642202</v>
+        <v>4.931724204542268</v>
       </c>
       <c r="N5" t="n">
-        <v>1082</v>
+        <v>-0.2990654205607477</v>
       </c>
       <c r="O5" t="n">
-        <v>218</v>
+        <v>-0.09882013873287143</v>
       </c>
       <c r="P5" t="n">
-        <v>1082</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="Q5" t="n">
-        <v>226</v>
+        <v>-0.3902439024390244</v>
       </c>
       <c r="R5" t="n">
-        <v>218</v>
+        <v>-0.1477272727272727</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9760105506323683</v>
+        <v>6.88653164253051</v>
       </c>
       <c r="T5" t="n">
-        <v>218</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="U5" t="n">
-        <v>1171</v>
+        <v>6.88653164253051</v>
       </c>
       <c r="V5" t="n">
-        <v>856</v>
+        <v>4.260798381942983</v>
       </c>
       <c r="W5" t="n">
-        <v>113.119405939032</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="X5" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>978</v>
+        <v>6.88653164253051</v>
       </c>
       <c r="Z5" t="n">
-        <v>1178</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2177232303965318</v>
+        <v>7.126087273299125</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="AC5" t="n">
-        <v>856</v>
+        <v>0.9951053111006976</v>
       </c>
       <c r="AD5" t="n">
-        <v>121.6799079552567</v>
+        <v>7.821242083523558</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.264018691588785</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="AF5" t="n">
-        <v>4.38178046004154</v>
+        <v>5.389071729816501</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.884486652042782</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>5.389071729816501</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>305</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1082</v>
+        <v>1.683019259953122</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2766393442622951</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>978</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F6" t="n">
-        <v>226</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1752336448598131</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H6" t="n">
-        <v>856</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="I6" t="n">
-        <v>1906</v>
+        <v>6.88653164253051</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03669724770642202</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="L6" t="n">
-        <v>706</v>
+        <v>1.726118501244531</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03669724770642202</v>
+        <v>4.809578588962567</v>
       </c>
       <c r="N6" t="n">
-        <v>1082</v>
+        <v>0.07954545454545459</v>
       </c>
       <c r="O6" t="n">
-        <v>218</v>
+        <v>-0.2177232303965318</v>
       </c>
       <c r="P6" t="n">
-        <v>1082</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="Q6" t="n">
-        <v>226</v>
+        <v>-0.1121495327102804</v>
       </c>
       <c r="R6" t="n">
-        <v>218</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9427611433904207</v>
+        <v>6.88653164253051</v>
       </c>
       <c r="T6" t="n">
-        <v>226</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="U6" t="n">
-        <v>1123</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="V6" t="n">
-        <v>706</v>
+        <v>4.737245320750187</v>
       </c>
       <c r="W6" t="n">
-        <v>194.1545775921843</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="X6" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>706</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="Z6" t="n">
-        <v>976</v>
+        <v>7.072421900537371</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.3334687789181868</v>
+        <v>7.066466970136958</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="AC6" t="n">
-        <v>706</v>
+        <v>0.9760105506323683</v>
       </c>
       <c r="AD6" t="n">
-        <v>143.7316944866363</v>
+        <v>7.821242083523558</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.278118609406953</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.38178046004154</v>
+        <v>5.389071729816501</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.75343791859778</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5.389071729816501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>309</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1082</v>
+        <v>1.683019259953122</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1542056074766355</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1082</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F7" t="n">
-        <v>226</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2597137014314929</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H7" t="n">
-        <v>978</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="I7" t="n">
-        <v>1388</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.1283018867924528</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03669724770642202</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="L7" t="n">
-        <v>706</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03669724770642202</v>
+        <v>4.974881645496656</v>
       </c>
       <c r="N7" t="n">
-        <v>1082</v>
+        <v>-0.2714285714285715</v>
       </c>
       <c r="O7" t="n">
-        <v>226</v>
+        <v>-0.3334687789181868</v>
       </c>
       <c r="P7" t="n">
-        <v>724</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="Q7" t="n">
-        <v>226</v>
+        <v>-0.4204545454545454</v>
       </c>
       <c r="R7" t="n">
-        <v>218</v>
+        <v>-0.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0.895839290734909</v>
+        <v>6.884486652042782</v>
       </c>
       <c r="T7" t="n">
-        <v>226</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="U7" t="n">
-        <v>1030</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="V7" t="n">
-        <v>706</v>
+        <v>5.273791950139548</v>
       </c>
       <c r="W7" t="n">
-        <v>212.0786017808794</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="X7" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>706</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="Z7" t="n">
-        <v>856</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.4443781781046132</v>
+        <v>7.024649030453636</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="AC7" t="n">
-        <v>706</v>
+        <v>0.9427611433904207</v>
       </c>
       <c r="AD7" t="n">
-        <v>162.0283925736468</v>
+        <v>7.553286605600419</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3308687615526802</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.577708763999919</v>
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.88653164253051</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>5.389071729816501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>310</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1082</v>
+        <v>1.521198603080359</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4008179959100204</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>706</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="F8" t="n">
-        <v>226</v>
+        <v>6.75343791859778</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4584103512014788</v>
+        <v>5.389071729816501</v>
       </c>
       <c r="H8" t="n">
-        <v>1082</v>
+        <v>6.88653164253051</v>
       </c>
       <c r="I8" t="n">
-        <v>1308</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="L8" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.093924373206255</v>
       </c>
       <c r="N8" t="n">
-        <v>724</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="O8" t="n">
-        <v>226</v>
+        <v>-0.4443781781046132</v>
       </c>
       <c r="P8" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>226</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="R8" t="n">
-        <v>222</v>
+        <v>-0.4736842105263158</v>
       </c>
       <c r="S8" t="n">
+        <v>6.75343791859778</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.561030665896573</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6.987490247000991</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.361661120082832</v>
+      </c>
+      <c r="W8" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.586171654854675</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.987490247000991</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>6.93828448401696</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.895839290734909</v>
       </c>
-      <c r="T8" t="n">
-        <v>226</v>
-      </c>
-      <c r="U8" t="n">
-        <v>977</v>
-      </c>
-      <c r="V8" t="n">
-        <v>586</v>
-      </c>
-      <c r="W8" t="n">
-        <v>75.01999733404095</v>
-      </c>
-      <c r="X8" t="n">
-        <v>226</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>586</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>978</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.4443781781046132</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.03669724770642202</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>586</v>
-      </c>
       <c r="AD8" t="n">
-        <v>206.4344932418025</v>
+        <v>7.236339342754344</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.169971671388102</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.987490247000991</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5.424950017481403</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>706</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.407171771460119</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.88653164253051</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.987490247000991</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.03669724770642202</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.334815594608298</v>
+      </c>
+      <c r="N9" t="n">
         <v>-0.4584103512014788</v>
       </c>
-      <c r="E9" t="n">
-        <v>724</v>
-      </c>
-      <c r="F9" t="n">
-        <v>226</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="O9" t="n">
+        <v>-0.4443781781046132</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.03669724770642202</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.4008179959100204</v>
+      </c>
+      <c r="R9" t="n">
         <v>-0.169971671388102</v>
       </c>
-      <c r="H9" t="n">
-        <v>706</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1178</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>586</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.03669724770642202</v>
-      </c>
-      <c r="N9" t="n">
-        <v>724</v>
-      </c>
-      <c r="O9" t="n">
-        <v>226</v>
-      </c>
-      <c r="P9" t="n">
-        <v>586</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>226</v>
-      </c>
-      <c r="R9" t="n">
-        <v>226</v>
-      </c>
       <c r="S9" t="n">
-        <v>0.8359254794186372</v>
+        <v>6.586171654854675</v>
       </c>
       <c r="T9" t="n">
-        <v>226</v>
+        <v>6.375024819828097</v>
       </c>
       <c r="U9" t="n">
-        <v>916</v>
+        <v>6.586171654854675</v>
       </c>
       <c r="V9" t="n">
-        <v>586</v>
+        <v>4.330996428491923</v>
       </c>
       <c r="W9" t="n">
-        <v>79.67433714816529</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="X9" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>586</v>
+        <v>6.586171654854675</v>
       </c>
       <c r="Z9" t="n">
-        <v>1082</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.548842958284719</v>
+        <v>6.885509670034818</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="AC9" t="n">
-        <v>586</v>
+        <v>0.895839290734909</v>
       </c>
       <c r="AD9" t="n">
-        <v>203.566205446778</v>
+        <v>7.1770187659099</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.1906077348066298</v>
+        <v>6.375024819828097</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.561030665896573</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>5.424950017481403</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3144475920679887</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>586</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="F10" t="n">
-        <v>226</v>
+        <v>6.987490247000991</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3314917127071824</v>
+        <v>5.424950017481403</v>
       </c>
       <c r="H10" t="n">
-        <v>724</v>
+        <v>6.561030665896573</v>
       </c>
       <c r="I10" t="n">
-        <v>1178</v>
+        <v>6.375024819828097</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.03460207612456756</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6.375024819828097</v>
       </c>
       <c r="L10" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03669724770642202</v>
+        <v>5.320891666105424</v>
       </c>
       <c r="N10" t="n">
-        <v>586</v>
+        <v>-0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>226</v>
+        <v>-0.548842958284719</v>
       </c>
       <c r="P10" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>226</v>
+        <v>-0.4933333333333333</v>
       </c>
       <c r="R10" t="n">
-        <v>226</v>
+        <v>-0.2549019607843137</v>
       </c>
       <c r="S10" t="n">
+        <v>6.561030665896573</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6.586171654854675</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.390420521581561</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.987490247000991</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.821107472256465</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.8359254794186372</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>7.072421900537371</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.586171654854675</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5.424950017481403</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.561030665896573</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.586171654854675</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.184148890937483</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.03460207612456756</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.184148890937483</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.602343991596719</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.09803921568627449</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.6453481132295501</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.5157894736842106</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.07999999999999996</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6.184148890937483</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.092504995545323</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.586171654854675</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.673297967767654</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AC11" t="n">
         <v>0.7638886127905428</v>
       </c>
-      <c r="T10" t="n">
-        <v>226</v>
-      </c>
-      <c r="U10" t="n">
-        <v>790</v>
-      </c>
-      <c r="V10" t="n">
-        <v>484</v>
-      </c>
-      <c r="W10" t="n">
-        <v>58.88972745733769</v>
-      </c>
-      <c r="X10" t="n">
-        <v>226</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>484</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>706</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.6453481132295501</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.03669724770642202</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>484</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>98.7177795536341</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.174061433447099</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
+      <c r="AD11" t="n">
+        <v>7.072421900537371</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6.184148890937483</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5.424950017481403</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>6.375024819828097</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5.424950017481403</v>
       </c>
     </row>
   </sheetData>
